--- a/tuition_export_with_compulsory.xlsx
+++ b/tuition_export_with_compulsory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoguelphca-my.sharepoint.com/personal/orscoop_uoguelph_ca/Documents/Desktop/Kunal Part time/Cost Calculator/Cost Calculcator architecture only/Frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_E0A4D15F0AD62394CA067D822619B267C1B2DDA3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3029ADB7-4B54-4D0A-8693-3708B239E40C}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_E0A4D15F0AD62394CA067D822619B267C1B2DDA3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B66818B6-A631-4E32-AAA8-D34912661292}"/>
   <bookViews>
-    <workbookView xWindow="-22050" yWindow="3705" windowWidth="21600" windowHeight="11175" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22395" yWindow="2790" windowWidth="21600" windowHeight="11175" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UG_Tuition" sheetId="1" r:id="rId1"/>
